--- a/artfynd/A 22044-2026 artfynd.xlsx
+++ b/artfynd/A 22044-2026 artfynd.xlsx
@@ -790,45 +790,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134225089</v>
+        <v>134217669</v>
       </c>
       <c r="B3" t="n">
-        <v>101386</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653540</v>
+        <v>653482</v>
       </c>
       <c r="R3" t="n">
-        <v>7003760</v>
+        <v>7003880</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,77 +861,100 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134217669</v>
+        <v>134225089</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>101388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653482</v>
+        <v>653540</v>
       </c>
       <c r="R4" t="n">
-        <v>7003880</v>
+        <v>7003760</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,55 +984,29 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
         <v>134225088</v>
       </c>
       <c r="B5" t="n">
-        <v>91968</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>134217622</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>134217619</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>134217624</v>
       </c>
       <c r="B9" t="n">
-        <v>92349</v>
+        <v>92351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>134225087</v>
       </c>
       <c r="B10" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>134217670</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>134217618</v>
       </c>
       <c r="B13" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>134217621</v>
       </c>
       <c r="B14" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>134225084</v>
       </c>
       <c r="B15" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>134225090</v>
       </c>
       <c r="B16" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>134217668</v>
       </c>
       <c r="B17" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>134225086</v>
       </c>
       <c r="B18" t="n">
-        <v>91968</v>
+        <v>91970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>134225085</v>
       </c>
       <c r="B19" t="n">
-        <v>98050</v>
+        <v>98052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22044-2026 artfynd.xlsx
+++ b/artfynd/A 22044-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217622</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217668</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217667</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217671</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225091</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225092</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217670</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225084</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217625</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,6 +2140,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225088</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2279,6 +2354,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217619</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2386,6 +2466,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217618</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2493,6 +2578,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217621</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225089</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2687,6 +2782,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225090</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2798,8 +2898,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>